--- a/artfynd/A 52104-2022 artfynd.xlsx
+++ b/artfynd/A 52104-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52104-2022 artfynd.xlsx
+++ b/artfynd/A 52104-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,132 +794,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Hälsinglands flora (2019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>82362015</v>
-      </c>
-      <c r="B3" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Lopplummer</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Långmor, Hls</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>568587.2209094719</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6876117.930989905</v>
-      </c>
-      <c r="S3" t="n">
-        <v>100</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>ALA198907040935</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>1989-07-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1989-07-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bäckdal och källa</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Björn Wannberg</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Arnold Larsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Hälsinglands flora (2019)</t>
         </is>
